--- a/excelprase/策划配置拷贝需要的到这里/ClientRoller.xlsx
+++ b/excelprase/策划配置拷贝需要的到这里/ClientRoller.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="821"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="821" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="c_roller" sheetId="25" r:id="rId1"/>
@@ -121,7 +121,7 @@
     <t>[{1,1,500},{2,501,1000}]</t>
   </si>
   <si>
-    <t>[5,3,6,2,2,2,9,8,3,1,6,6,6,8,7,6,4,4,2,4,11,6,2,8,1,3,1,7,7,6,6,6,6,23,1,9,9,9,9,6,1,6,3,2,1,1,1,5,1,4,4,7,2,5,5,12,23,6,2,3,2,7,1,1,6,6,6,4,4,7,7,9,4,12,1,23,2,2,2,3,3,1,2,1,1,1,1,7,1,6,8,8,1,3,8,1,21,1,1,1,1,4,4,5,13,3,8,4,3,3,3,2,2,2,9,6,2,5,4,23,2,1,1,1,3,3,7,7,9,3,4,4,23,2,2,5,5,5,5,3,3,3,1,8,8,8,7,7,7,7,8,7,9,8,6,7,7,6,8,13,3,3,23,1,1,5,5,5,5,4,1,1,1,4,1,6,6,4,2,14,3,3,3,2,7,15,1,1,1,3,1,4,4,4,4,5,5,1,1,2,2,1,1,1,1,16,2,2,3,3,3,5,5,4,4,4,4,5,5,5,5,2,2,8,2,1,5,5,8,8,7,2,6,6,6,7,7,7,1,8,8,5,1,23,1,1,9,7,9,9,3,1,2,7,1,3,3,3,1,2,2,2,3,5,4,4,4,5,5,1,1,1,1,3,3,4,2,7,6,6,2,2,5,4,1,3,5,9,9,9,9,5,2,2,2,23,9,9,1,1,1,2,2,2,1,4,4,4,5,7,8,6,9,9,5,6,1,1,1,1,1,5,6,6,8,2,2,3,3,7,7,9,5,9,9,9,3,23,1,1,1,5,5,5,5,3,3,3,5,5,5,4,4,9,1,9,9,9,5,4,7,8,8,4,4,4,6,4,4,2,6,4,4,4,8,8,6,7,7,6,8,8,1,6,1,7,8,7,4,1,4,1,8,3,2,6,6,6,6,4,2,2,5,5,7,1,1,1,6,6,4,3,2,6,1,7,2,3,3,6,6,6,6,10,1,2,2,1,1,7,1,2,4,5,8,2,1,1,4,4,7,7,3,1,13,1,2,4,3,7,5,5,3,3,3,3,1,3,3,15,3,2,1,7,5,5,3,6,6,8,2,2,2,2,1,2,1,7,7,1,1,8,3,8,7,5,4,4,8,3,3,2,2,8,1,8,7,8,3,8,2,2,9,2,5,5,3,3,3,4,7,1,1,7,4,4,4,7,2,8,6,5,5,5,2,5,5,1,2,2,3,5,1,7,1,7,3,3,3,7,7,2,2,8,8,9,5,4,8,8,4,4,6,6,1,8,1,1,2,2,2,4,5,5,5,6,6,2,4,1,4,8,2,2,2,2,1,6,6,9,5,5,9,1,1,1,7,8,7,3,3,4,3,7,8,1,8,5,7,7,9,9,4,1,1,8,7,7,2,6,7,7,7,7,5,5,5,5,7,7,6,1,1,3,2,1,1,18,4,4,4,5,8,6,6,13,3,9,9,1,8,8,3,3,3,5,2,9,9,1,1,2,3,1,1,3,8,5,2,4,3,4,3,6,8,2,2,6,6,1,6,6,6,3,1,3,2,2,2,6,6,6,6,8,1,15,1,6,8,3,4,4,1,1,1,5,5,8,7,7,17,2,8,8,1,1,2,2,9,1,8,8,2,1,6,6,3,3,3,1,1,4,1,15,9,4,3,3,3,6,7,14,1,1,8,5,9,9,1,15,3,7,9,9,11,4,8,4,4,14,3,3,3,4,8,8,8,1,1,7,5,2,19,1,6,1,6,3,3,3,6,7,8,2,5,2,12,4,4,3,2,15,4,2,1,3,3,3,5,2,10,5,3,3,1,6,1,1,6,7,1,1,4,4,2,2,5,1,7,4,1,1,1,2,2,7,17,1,5,1,3,1,1,4,4,4,8,5,5,4,2,10,4,12,7,1,1,3,1,8,1,1,8,8,1,1,5,5,5,1,1,6,3,2,1,4,2,2,3,9,9,9,1,1,8,8,5,7,7,2,3,3,10,5,4,4,7,7,7,4,4,2,6,2,4,4,6,6,1,1,6,8,6,3,4,5,4,2,2,2,7,2,6,6,2,2,7,2,5,8,8,8,6,10,6,7,6,6,3,2,3,3,4,4,1,5,11,1,3,2,2,8,8,3,1,6,1,4,7,2,5,5,1,10,2,1,2,6,6,6,1,1,2,7,10,3,7,6,6,1,4,3,3,1,2,2,9,9,6,6,7,7,7,3,1,1,3,2,1,2,2,1,5,5,1,5,2,3,7,5,5,8,1,1,1,2,2,8,5,17]</t>
+    <t>[5,3,6,2,2,2,9,8,3,1,6,6,6,8,7,6,4,4,2,4,11,6,2,8,1,3,1,7,7,6,6,6,6,2,1,9,9,9,9,6,1,6,3,2,1,1,1,5,1,4,4,7,2,5,5,12,2,6,2,3,2,7,1,1,6,6,6,4,4,7,7,9,4,12,1,2,2,2,2,3,3,1,2,1,1,1,1,7,1,6,8,8,1,3,8,1,21,1,1,1,1,4,4,5,13,3,8,4,3,3,3,2,2,2,9,6,2,5,4,2,2,1,1,1,3,3,7,7,9,3,4,4,2,2,2,5,5,5,5,3,3,3,1,8,8,8,7,7,7,7,8,7,9,8,6,7,7,6,8,13,3,3,2,1,1,5,5,5,5,4,1,1,1,4,1,6,6,4,2,14,3,3,3,2,7,15,1,1,1,3,1,4,4,4,4,5,5,1,1,2,2,1,1,1,1,16,2,2,3,3,3,5,5,4,4,4,4,5,5,5,5,2,2,8,2,1,5,5,8,8,7,2,6,6,6,7,7,7,1,8,8,5,1,2,1,1,9,7,9,9,3,1,2,7,1,3,3,3,1,2,2,2,3,5,4,4,4,5,5,1,1,1,1,3,3,4,2,7,6,6,2,2,5,4,1,3,5,9,9,9,9,5,2,2,2,2,9,9,1,1,1,2,2,2,1,4,4,4,5,7,8,6,9,9,5,6,1,1,1,1,1,5,6,6,8,2,2,3,3,7,7,9,5,9,9,9,3,2,1,1,1,5,5,5,5,3,3,3,5,5,5,4,4,9,1,9,9,9,5,4,7,8,8,4,4,4,6,4,4,2,6,4,4,4,8,8,6,7,7,6,8,8,1,6,1,7,8,7,4,1,4,1,8,3,2,6,6,6,6,4,2,2,5,5,7,1,1,1,6,6,4,3,2,6,1,7,2,3,3,6,6,6,6,10,1,2,2,1,1,7,1,2,4,5,8,2,1,1,4,4,7,7,3,1,13,1,2,4,3,7,5,5,3,3,3,3,1,3,3,15,3,2,1,7,5,5,3,6,6,8,2,2,2,2,1,2,1,7,7,1,1,8,3,8,7,5,4,4,8,3,3,2,2,8,1,8,7,8,3,8,2,2,9,2,5,5,3,3,3,4,7,1,1,7,4,4,4,7,2,8,6,5,5,5,2,5,5,1,2,2,3,5,1,7,1,7,3,3,3,7,7,2,2,8,8,9,5,4,8,8,4,4,6,6,1,8,1,1,2,2,2,4,5,5,5,6,6,2,4,1,4,8,2,2,2,2,1,6,6,9,5,5,9,1,1,1,7,8,7,3,3,4,3,7,8,1,8,5,7,7,9,9,4,1,1,8,7,7,2,6,7,7,7,7,5,5,5,5,7,7,6,1,1,3,2,1,1,18,4,4,4,5,8,6,6,13,3,9,9,1,8,8,3,3,3,5,2,9,9,1,1,2,3,1,1,3,8,5,2,4,3,4,3,6,8,2,2,6,6,1,6,6,6,3,1,3,2,2,2,6,6,6,6,8,1,15,1,6,8,3,4,4,1,1,1,5,5,8,7,7,17,2,8,8,1,1,2,2,9,1,8,8,2,1,6,6,3,3,3,1,1,4,1,15,9,4,3,3,3,6,7,14,1,1,8,5,9,9,1,15,3,7,9,9,11,4,8,4,4,14,3,3,3,4,8,8,8,1,1,7,5,2,19,1,6,1,6,3,3,3,6,7,8,2,5,2,12,4,4,3,2,15,4,2,1,3,3,3,5,2,10,5,3,3,1,6,1,1,6,7,1,1,4,4,2,2,5,1,7,4,1,1,1,2,2,7,17,1,5,1,3,1,1,4,4,4,8,5,5,4,2,10,4,12,7,1,1,3,1,8,1,1,8,8,1,1,5,5,5,1,1,6,3,2,1,4,2,2,3,9,9,9,1,1,8,8,5,7,7,2,3,3,10,5,4,4,7,7,7,4,4,2,6,2,4,4,6,6,1,1,6,8,6,3,4,5,4,2,2,2,7,2,6,6,2,2,7,2,5,8,8,8,6,10,6,7,6,6,3,2,3,3,4,4,1,5,11,1,3,2,2,8,8,3,1,6,1,4,7,2,5,5,1,10,2,1,2,6,6,6,1,1,2,7,10,3,7,6,6,1,4,3,3,1,2,2,9,9,6,6,7,7,7,3,1,1,3,2,1,2,2,1,5,5,1,5,2,3,7,5,5,8,1,1,1,2,2,8,5,17]</t>
   </si>
   <si>
     <t>100100_2</t>
@@ -130,7 +130,7 @@
     <t>[[18,12,12,12]]</t>
   </si>
   <si>
-    <t>[2,7,7,7,7,1,3,9,5,5,5,5,1,8,12,2,2,2,1,1,3,1,23,5,5,5,1,1,1,4,2,9,9,8,7,8,13,2,2,9,1,3,9,2,6,1,2,2,6,6,4,4,2,1,6,6,1,4,8,18,5,5,5,5,2,4,1,8,23,4,4,4,5,5,5,5,7,7,1,9,6,1,3,16,4,7,5,2,7,7,4,6,6,6,6,3,3,3,3,1,1,9,4,4,2,16,8,6,2,4,4,1,7,7,1,1,3,1,4,4,1,1,1,1,6,4,8,8,8,1,3,14,9,3,1,1,3,3,3,8,8,7,1,9,6,1,1,1,7,3,6,3,3,13,23,1,5,5,8,8,1,1,5,1,1,3,3,2,2,7,7,7,4,4,2,2,2,5,15,9,3,2,6,4,3,3,1,2,7,1,4,6,6,1,7,7,3,3,2,1,1,2,17,5,1,5,5,23,6,8,3,2,6,2,9,4,23,6,6,6,2,3,5,7,7,1,2,2,1,9,9,3,3,1,1,1,2,8,1,9,2,2,2,4,23,1,6,8,1,15,4,8,1,1,1,3,2,2,5,5,2,6,9,7,7,7,5,5,7,7,7,7,3,3,3,10,5,5,5,2,4,4,4,6,1,1,2,1,23,3,6,6,6,2,4,3,3,3,3,1,1,9,9,6,6,2,4,4,4,4,1,1,7,2,2,2,1,7,3,1,3,3,6,15,1,1,1,3,2,2,1,3,3,5,9,9,5,9,14,4,4,4,5,5,5,5,8,8,8,8,23,2,2,8,1,8,8,8,14,4,4,1,1,2,6,9,3,4,4,15,1,1,1,7,8,3,3,3,3,2,1,6,4,2,2,18,5,5,5,1,5,8,3,2,1,7,1,1,1,5,5,8,4,7,7,7,6,3,13,9,1,3,3,6,2,5,5,9,9,1,6,2,7,5,1,4,3,3,3,1,3,2,4,9,6,1,4,6,4,5,4,2,9,9,1,7,2,2,23,1,8,5,5,8,8,3,3,6,6,1,17,1,7,2,2,2,2,9,7,7,4,6,6,1,8,1,6,6,9,9,8,8,3,1,2,7,23,2,6,6,6,1,1,4,1,1,4,4,1,2,5,8,8,8,2,2,4,2,23,3,4,4,4,4,3,3,3,6,1,2,8,2,7,7,8,8,1,7,2,6,7,7,6,6,1,6,6,9,9,9,8,2,2,7,9,9,9,7,9,9,9,3,9,4,1,1,8,5,4,7,1,1,5,5,5,9,9,9,1,1,1,1,1,5,5,5,4,1,6,2,2,2,1,6,6,2,2,6,6,1,5,3,3,7,6,6,4,4,4,4,7,3,3,7,1,7,7,7,3,1,1,4,4,4,9,5,5,6,6,2,3,3,5,5,8,8,4,4,1,3,3,3,3,1,4,4,2,1,5,1,15,5,5,4,1,1,2,4,1,1,8,2,1,1,3,6,6,1,1,2,2,5,4,8,2,2,2,7,3,7,1,6,22,2,1,4,12,3,3,2,3,3,6,2,2,1,1,6,5,5,5,2,8,8,8,8,3,3,7,7,2,4,5,4,3,1,8,8,6,1,3,5,8,1,1,3,3,3,1,1,2,2,6,1,1,18,8,5,6,1,8,8,6,6,1,1,7,7,1,8,9,9,7,8,1,7,7,5,7,7,1,1,3,2,4,4,3,8,8,8,3,9,4,6,6,3,3,4,2,8,7,2,7,23,3,3,8,1,5,6,4,4,2,5,1,5,5,1,1,4,10,1,4,5,5,1,1,6,1,1,1,3,2,4,4,6,17,2,3,7,7,1,2,1,1,8,2,2,23,1,5,5,4,4,4,7,8,8,3,1,6,10,4,7,9,4,4,2,2,1,5,5,2,7,7,7,2,6,6,1,7,7,16,4,1,4,3,2,3,7,7,1,5,1,4,5,7,5,8,5,1,23,10,3,6,8,1,3,2,4,3,5,5,2,2,1,6,2,1,1,6,6,6,2,2,3,2,8,6,3,3,2,8,2,6,1,3,3,3,2,1,1,1,10,2,23,7,1,1,1,2,2,1,5,1,1,1,1,2,2,1,5,7,7,7,1,1,7,7,6,4,4,9,3,3,6,5,2,2,1,4,6,6,6,10,2,2,5,2,1,1,3,1,23,5,5,5,8,7,1,1,4,1,3,6,5,6,8,3,3,8,8,1,1,6,6,7,5,2,2,1,23,3,8,1,2,9,8,4,19]</t>
+    <t>[2,7,7,7,7,1,3,9,5,5,5,5,1,8,12,2,2,2,1,1,3,1,2,5,5,5,1,1,1,4,2,9,9,8,7,8,13,2,2,9,1,3,9,2,6,1,2,2,6,6,4,4,2,1,6,6,1,4,8,18,5,5,5,5,2,4,1,8,2,4,4,4,5,5,5,5,7,7,1,9,6,1,3,16,4,7,5,2,7,7,4,6,6,6,6,3,3,3,3,1,1,9,4,4,2,16,8,6,2,4,4,1,7,7,1,1,3,1,4,4,1,1,1,1,6,4,8,8,8,1,3,14,9,3,1,1,3,3,3,8,8,7,1,9,6,1,1,1,7,3,6,3,3,13,2,1,5,5,8,8,1,1,5,1,1,3,3,2,2,7,7,7,4,4,2,2,2,5,15,9,3,2,6,4,3,3,1,2,7,1,4,6,6,1,7,7,3,3,2,1,1,2,17,5,1,5,5,2,6,8,3,2,6,2,9,4,2,6,6,6,2,3,5,7,7,1,2,2,1,9,9,3,3,1,1,1,2,8,1,9,2,2,2,4,2,1,6,8,1,15,4,8,1,1,1,3,2,2,5,5,2,6,9,7,7,7,5,5,7,7,7,7,3,3,3,10,5,5,5,2,4,4,4,6,1,1,2,1,2,3,6,6,6,2,4,3,3,3,3,1,1,9,9,6,6,2,4,4,4,4,1,1,7,2,2,2,1,7,3,1,3,3,6,15,1,1,1,3,2,2,1,3,3,5,9,9,5,9,14,4,4,4,5,5,5,5,8,8,8,8,2,2,2,8,1,8,8,8,14,4,4,1,1,2,6,9,3,4,4,15,1,1,1,7,8,3,3,3,3,2,1,6,4,2,2,18,5,5,5,1,5,8,3,2,1,7,1,1,1,5,5,8,4,7,7,7,6,3,13,9,1,3,3,6,2,5,5,9,9,1,6,2,7,5,1,4,3,3,3,1,3,2,4,9,6,1,4,6,4,5,4,2,9,9,1,7,2,2,2,1,8,5,5,8,8,3,3,6,6,1,17,1,7,2,2,2,2,9,7,7,4,6,6,1,8,1,6,6,9,9,8,8,3,1,2,7,2,2,6,6,6,1,1,4,1,1,4,4,1,2,5,8,8,8,2,2,4,2,2,3,4,4,4,4,3,3,3,6,1,2,8,2,7,7,8,8,1,7,2,6,7,7,6,6,1,6,6,9,9,9,8,2,2,7,9,9,9,7,9,9,9,3,9,4,1,1,8,5,4,7,1,1,5,5,5,9,9,9,1,1,1,1,1,5,5,5,4,1,6,2,2,2,1,6,6,2,2,6,6,1,5,3,3,7,6,6,4,4,4,4,7,3,3,7,1,7,7,7,3,1,1,4,4,4,9,5,5,6,6,2,3,3,5,5,8,8,4,4,1,3,3,3,3,1,4,4,2,1,5,1,15,5,5,4,1,1,2,4,1,1,8,2,1,1,3,6,6,1,1,2,2,5,4,8,2,2,2,7,3,7,1,6,22,2,1,4,12,3,3,2,3,3,6,2,2,1,1,6,5,5,5,2,8,8,8,8,3,3,7,7,2,4,5,4,3,1,8,8,6,1,3,5,8,1,1,3,3,3,1,1,2,2,6,1,1,18,8,5,6,1,8,8,6,6,1,1,7,7,1,8,9,9,7,8,1,7,7,5,7,7,1,1,3,2,4,4,3,8,8,8,3,9,4,6,6,3,3,4,2,8,7,2,7,2,3,3,8,1,5,6,4,4,2,5,1,5,5,1,1,4,10,1,4,5,5,1,1,6,1,1,1,3,2,4,4,6,17,2,3,7,7,1,2,1,1,8,2,2,2,1,5,5,4,4,4,7,8,8,3,1,6,10,4,7,9,4,4,2,2,1,5,5,2,7,7,7,2,6,6,1,7,7,16,4,1,4,3,2,3,7,7,1,5,1,4,5,7,5,8,5,1,2,10,3,6,8,1,3,2,4,3,5,5,2,2,1,6,2,1,1,6,6,6,2,2,3,2,8,6,3,3,2,8,2,6,1,3,3,3,2,1,1,1,10,2,2,7,1,1,1,2,2,1,5,1,1,1,1,2,2,1,5,7,7,7,1,1,7,7,6,4,4,9,3,3,6,5,2,2,1,4,6,6,6,10,2,2,5,2,1,1,3,1,2,5,5,5,8,7,1,1,4,1,3,6,5,6,8,3,3,8,8,1,1,6,6,7,5,2,2,1,2,3,8,1,2,9,8,4,19]</t>
   </si>
   <si>
     <t>100100_3</t>
@@ -139,7 +139,7 @@
     <t>[[17,12,12,12]]</t>
   </si>
   <si>
-    <t>[3,4,4,4,3,5,8,6,7,7,2,2,2,2,3,3,1,4,14,1,6,6,2,4,4,1,2,2,8,5,5,5,5,3,1,2,2,6,6,2,2,2,2,3,23,6,2,6,8,3,8,1,3,6,6,2,3,3,1,1,8,23,5,5,1,1,1,5,6,1,3,6,1,6,9,2,2,2,7,7,1,4,1,7,7,7,7,8,8,8,8,3,23,6,7,7,7,7,1,1,1,5,5,7,1,7,1,4,4,23,6,5,9,9,1,7,5,2,7,4,7,9,9,3,7,7,2,4,4,1,3,2,3,3,8,8,8,8,1,1,3,2,1,1,6,6,1,1,1,2,2,5,2,23,5,5,5,5,6,5,1,6,6,6,6,1,9,1,1,1,3,1,4,6,1,1,3,1,4,1,1,1,4,1,1,4,4,2,2,7,7,7,1,4,4,2,2,8,8,1,1,1,16,4,4,4,3,8,5,1,5,5,9,9,3,3,1,1,3,2,1,3,4,5,5,5,5,1,2,1,6,6,3,1,8,2,2,2,2,3,3,2,9,2,1,1,1,2,1,1,1,1,1,2,2,7,1,5,5,5,6,5,7,9,9,2,8,5,5,5,4,5,1,1,7,7,7,2,8,8,2,2,2,2,1,4,4,6,4,4,4,7,2,1,1,2,8,1,2,7,4,4,4,1,1,13,3,3,3,1,3,6,6,6,7,7,4,6,4,1,9,1,7,6,8,7,7,7,7,4,1,3,5,6,4,7,7,5,3,5,2,1,5,5,5,5,4,6,1,9,9,3,3,3,1,3,4,2,3,3,3,6,6,8,3,3,3,8,8,8,1,5,1,1,4,4,8,9,9,5,5,1,1,3,7,7,2,1,2,1,1,1,1,9,4,4,4,4,1,8,9,9,1,1,3,6,2,2,6,2,3,6,9,1,9,2,2,2,1,1,1,1,3,2,1,2,4,8,2,2,8,3,8,8,9,9,2,5,7,6,2,8,8,2,5,3,5,8,3,2,5,5,5,5,6,3,3,9,4,1,4,1,3,2,6,4,1,4,4,1,2,4,3,2,2,3,3,3,6,2,6,3,1,1,1,6,6,2,5,9,9,6,6,7,1,6,7,8,3,14,6,6,6,6,5,3,3,4,2,2,8,4,4,5,1,1,7,9,1,6,8,1,6,4,4,9,9,9,9,3,2,2,2,17,1,5,5,2,2,1,1,1,7,7,2,2,9,4,5,5,3,6,3,3,2,2,4,6,8,7,7,1,3,2,6,6,8,1,1,1,5,1,15,2,2,2,1,1,1,1,3,3,3,4,4,2,2,2,5,5,5,5,3,7,1,16,5,4,8,8,8,8,4,2,1,1,5,4,6,6,6,6,7,7,7,8,8,1,2,2,6,4,4,4,4,8,3,3,3,8,6,6,6,6,3,1,3,3,2,1,12,2,2,2,8,6,6,3,3,8,4,9,6,9,5,5,5,5,4,4,1,3,1,7,9,2,12,8,8,8,1,1,9,9,1,7,7,3,5,5,1,5,5,5,3,2,1,1,1,7,2,2,2,4,4,3,3,3,7,7,1,1,5,5,3,3,1,1,7,1,9,8,9,9,13,9,9,4,1,7,7,7,3,1,1,1,4,4,1,6,8,8,8,6,3,1,1,8,3,7,7,7,8,4,1,8,6,8,7,7,4,2,2,2,3,1,3,3,8,8,5,6,6,5,8,2,2,17,8,8,2,4,6,6,7,7,7,2,2,4,7,1,1,5,1,5,2,6,1,8,10,8,2,2,7,8,3,3,1,1,2,5,4,9,9,1,1,9,9,2,8,1,7,6,6,2,1,4,2,1,3,6,6,5,5,5,1,1,5,5,8,10,1,7,3,5,5,5,3,1,4,1,1,1,3,6,7,7,3,2,1,5,5,2,1,2,6,1,2,6,21,1,4,3,1,4,3,3,1,6,6,5,10,5,1,1,4,14,2,5,5,7,7,1,1,1,2,4,1,10,1,4,8,1,4,4,2,8,6,6,7,7,4,4,4,2,2,2,5,3,2,2,7,10,4,4,4,2,7,4,4,6,1,2,1,2,4,4,3,3,1,3,5,8,3,7,8,6,1,1,5,5,3,6,3,3,1,1,6,7,7,7,2,23,10,1,5,3,4,1,3,6,1,1,1,3,2,2,6,6,6,1,1,9,1,3,7,5,2,6,8,7,2,8,3,2,3,7,1,2,8,1,1,2,1,8,3,1,2,23]</t>
+    <t>[3,4,4,4,3,5,8,6,7,7,2,2,2,2,3,3,1,4,14,1,6,6,2,4,4,1,2,2,8,5,5,5,5,3,1,2,2,6,6,2,2,2,2,3,2,6,2,6,8,3,8,1,3,6,6,2,3,3,1,1,8,2,5,5,1,1,1,5,6,1,3,6,1,6,9,2,2,2,7,7,1,4,1,7,7,7,7,8,8,8,8,3,2,6,7,7,7,7,1,1,1,5,5,7,1,7,1,4,4,2,6,5,9,9,1,7,5,2,7,4,7,9,9,3,7,7,2,4,4,1,3,2,3,3,8,8,8,8,1,1,3,2,1,1,6,6,1,1,1,2,2,5,2,2,5,5,5,5,6,5,1,6,6,6,6,1,9,1,1,1,3,1,4,6,1,1,3,1,4,1,1,1,4,1,1,4,4,2,2,7,7,7,1,4,4,2,2,8,8,1,1,1,16,4,4,4,3,8,5,1,5,5,9,9,3,3,1,1,3,2,1,3,4,5,5,5,5,1,2,1,6,6,3,1,8,2,2,2,2,3,3,2,9,2,1,1,1,2,1,1,1,1,1,2,2,7,1,5,5,5,6,5,7,9,9,2,8,5,5,5,4,5,1,1,7,7,7,2,8,8,2,2,2,2,1,4,4,6,4,4,4,7,2,1,1,2,8,1,2,7,4,4,4,1,1,13,3,3,3,1,3,6,6,6,7,7,4,6,4,1,9,1,7,6,8,7,7,7,7,4,1,3,5,6,4,7,7,5,3,5,2,1,5,5,5,5,4,6,1,9,9,3,3,3,1,3,4,2,3,3,3,6,6,8,3,3,3,8,8,8,1,5,1,1,4,4,8,9,9,5,5,1,1,3,7,7,2,1,2,1,1,1,1,9,4,4,4,4,1,8,9,9,1,1,3,6,2,2,6,2,3,6,9,1,9,2,2,2,1,1,1,1,3,2,1,2,4,8,2,2,8,3,8,8,9,9,2,5,7,6,2,8,8,2,5,3,5,8,3,2,5,5,5,5,6,3,3,9,4,1,4,1,3,2,6,4,1,4,4,1,2,4,3,2,2,3,3,3,6,2,6,3,1,1,1,6,6,2,5,9,9,6,6,7,1,6,7,8,3,14,6,6,6,6,5,3,3,4,2,2,8,4,4,5,1,1,7,9,1,6,8,1,6,4,4,9,9,9,9,3,2,2,2,17,1,5,5,2,2,1,1,1,7,7,2,2,9,4,5,5,3,6,3,3,2,2,4,6,8,7,7,1,3,2,6,6,8,1,1,1,5,1,15,2,2,2,1,1,1,1,3,3,3,4,4,2,2,2,5,5,5,5,3,7,1,16,5,4,8,8,8,8,4,2,1,1,5,4,6,6,6,6,7,7,7,8,8,1,2,2,6,4,4,4,4,8,3,3,3,8,6,6,6,6,3,1,3,3,2,1,12,2,2,2,8,6,6,3,3,8,4,9,6,9,5,5,5,5,4,4,1,3,1,7,9,2,12,8,8,8,1,1,9,9,1,7,7,3,5,5,1,5,5,5,3,2,1,1,1,7,2,2,2,4,4,3,3,3,7,7,1,1,5,5,3,3,1,1,7,1,9,8,9,9,13,9,9,4,1,7,7,7,3,1,1,1,4,4,1,6,8,8,8,6,3,1,1,8,3,7,7,7,8,4,1,8,6,8,7,7,4,2,2,2,3,1,3,3,8,8,5,6,6,5,8,2,2,17,8,8,2,4,6,6,7,7,7,2,2,4,7,1,1,5,1,5,2,6,1,8,10,8,2,2,7,8,3,3,1,1,2,5,4,9,9,1,1,9,9,2,8,1,7,6,6,2,1,4,2,1,3,6,6,5,5,5,1,1,5,5,8,10,1,7,3,5,5,5,3,1,4,1,1,1,3,6,7,7,3,2,1,5,5,2,1,2,6,1,2,6,21,1,4,3,1,4,3,3,1,6,6,5,10,5,1,1,4,14,2,5,5,7,7,1,1,1,2,4,1,10,1,4,8,1,4,4,2,8,6,6,7,7,4,4,4,2,2,2,5,3,2,2,7,10,4,4,4,2,7,4,4,6,1,2,1,2,4,4,3,3,1,3,5,8,3,7,8,6,1,1,5,5,3,6,3,3,1,1,6,7,7,7,2,2,10,1,5,3,4,1,3,6,1,1,1,3,2,2,6,6,6,1,1,9,1,3,7,5,2,6,8,7,2,8,3,2,3,7,1,2,8,1,1,2,1,8,3,1,2,2]</t>
   </si>
   <si>
     <t>100100_4</t>
@@ -148,7 +148,7 @@
     <t>[[16,12,12,12]]</t>
   </si>
   <si>
-    <t>[6,2,2,1,9,2,1,7,2,4,18,8,8,4,2,2,2,2,1,1,2,2,5,7,7,8,1,1,1,7,8,8,7,7,2,7,3,1,2,1,1,6,6,9,9,9,7,4,1,7,7,7,6,1,5,5,5,13,1,1,3,3,8,8,8,4,2,3,1,1,1,1,8,8,6,6,6,4,4,5,5,1,7,7,1,5,1,1,1,1,3,4,4,5,8,3,7,2,9,2,2,2,1,3,1,1,2,3,17,7,8,5,4,4,4,7,2,6,2,3,3,3,1,9,9,7,7,7,1,1,3,4,1,1,12,5,8,12,3,4,4,1,1,1,6,5,5,5,5,1,9,1,5,5,1,1,3,5,2,3,6,1,7,1,1,3,5,4,6,7,7,6,6,2,1,1,1,1,2,1,1,2,3,4,2,6,3,3,23,3,2,1,6,3,2,3,4,1,1,1,4,4,4,4,1,8,3,3,3,3,6,6,9,5,9,6,1,2,2,2,1,1,1,9,4,5,5,6,5,4,8,2,5,6,2,23,3,8,6,4,8,2,4,5,6,1,6,2,5,2,6,1,2,3,2,19,8,2,8,7,7,2,5,5,7,4,7,7,1,1,1,9,9,1,1,4,1,1,4,3,3,5,6,3,1,2,5,3,8,8,8,18,4,9,6,4,9,9,4,1,1,2,5,17,7,7,7,5,5,5,2,2,2,6,1,1,6,1,3,1,3,2,1,1,9,9,3,2,2,2,6,6,6,1,5,5,5,5,3,4,9,9,2,2,7,7,7,7,3,3,19,5,5,1,1,4,16,6,3,5,5,5,6,2,2,5,5,18,8,2,1,1,2,2,1,2,2,2,5,5,5,5,8,8,8,1,1,4,8,1,7,2,1,4,4,1,1,1,1,4,8,8,4,4,6,4,8,3,8,3,3,3,3,4,1,1,2,9,1,8,8,7,7,7,1,4,4,4,6,6,4,4,4,9,9,9,2,3,7,1,1,1,1,3,3,19,7,7,7,13,2,2,6,3,6,1,5,4,3,1,3,3,2,3,5,3,6,1,2,2,2,1,4,6,6,6,2,6,6,6,6,3,5,4,1,4,3,12,4,3,4,2,4,4,1,3,3,8,2,12,9,7,5,1,9,8,1,8,5,5,4,4,3,3,3,4,4,3,3,2,5,7,7,7,1,1,1,1,9,8,1,1,4,4,1,2,5,4,1,1,1,4,2,2,1,6,15,5,7,7,2,2,4,4,3,3,8,8,1,6,6,3,4,4,9,8,8,8,7,1,7,7,1,1,1,23,5,5,5,6,4,4,7,5,5,3,3,4,3,9,9,19,8,3,3,3,1,2,2,7,7,3,5,6,1,4,4,4,2,2,7,7,3,3,4,4,1,5,4,3,6,6,4,6,6,2,7,16,6,6,6,9,9,5,7,7,2,6,6,1,6,16,9,8,8,4,4,4,9,9,3,2,7,6,6,6,6,5,5,5,8,18,6,1,1,1,1,23,2,2,7,1,8,8,1,1,2,5,5,3,3,3,1,2,2,2,3,23,5,2,1,1,2,2,7,1,1,3,1,2,2,6,6,2,8,2,2,2,23,1,8,7,7,3,3,7,2,1,7,3,1,5,8,1,3,8,8,1,1,1,9,9,9,8,8,15,5,5,1,1,8,8,6,4,1,7,8,1,1,1,2,2,3,3,10,5,5,5,7,8,7,8,1,1,4,3,6,6,2,2,6,6,6,3,3,2,1,8,3,3,3,1,1,1,1,8,2,3,23,2,10,2,2,5,5,1,8,4,1,6,7,7,7,3,3,5,1,1,6,9,9,9,6,1,1,1,4,4,6,1,5,1,1,5,5,5,2,1,1,1,5,10,3,23,1,1,6,6,6,7,1,1,3,3,16,1,1,2,2,1,1,9,5,4,1,4,4,2,2,5,2,6,6,2,5,5,4,7,1,3,2,2,10,2,4,4,4,1,1,2,3,7,7,2,2,5,4,4,4,1,1,1,17,7,2,8,1,8,1,8,8,7,7,3,9,3,3,5,1,1,1,7,1,10,6,1,4,7,2,4,4,6,4,6,1,6,5,1,1,2,2,3,3,5,2,3,5,1,5,6,23,7,7,5,5,5,23,3,3,2,12,7,6,1,10,1,1,4,8,1,4,8,2,2,3,3,8,7,5,2,7,7,2,2,4,4,8,1,4,4,3,3,8,8,2,2,8,6,6,6,8,4,2,7,1,2,1,8,6,17]</t>
+    <t>[6,2,2,1,9,2,1,7,2,4,18,8,8,4,2,2,2,2,1,1,2,2,5,7,7,8,1,1,1,7,8,8,7,7,2,7,3,1,2,1,1,6,6,9,9,9,7,4,1,7,7,7,6,1,5,5,5,13,1,1,3,3,8,8,8,4,2,3,1,1,1,1,8,8,6,6,6,4,4,5,5,1,7,7,1,5,1,1,1,1,3,4,4,5,8,3,7,2,9,2,2,2,1,3,1,1,2,3,17,7,8,5,4,4,4,7,2,6,2,3,3,3,1,9,9,7,7,7,1,1,3,4,1,1,12,5,8,12,3,4,4,1,1,1,6,5,5,5,5,1,9,1,5,5,1,1,3,5,2,3,6,1,7,1,1,3,5,4,6,7,7,6,6,2,1,1,1,1,2,1,1,2,3,4,2,6,3,3,2,3,2,1,6,3,2,3,4,1,1,1,4,4,4,4,1,8,3,3,3,3,6,6,9,5,9,6,1,2,2,2,1,1,1,9,4,5,5,6,5,4,8,2,5,6,2,2,3,8,6,4,8,2,4,5,6,1,6,2,5,2,6,1,2,3,2,19,8,2,8,7,7,2,5,5,7,4,7,7,1,1,1,9,9,1,1,4,1,1,4,3,3,5,6,3,1,2,5,3,8,8,8,18,4,9,6,4,9,9,4,1,1,2,5,17,7,7,7,5,5,5,2,2,2,6,1,1,6,1,3,1,3,2,1,1,9,9,3,2,2,2,6,6,6,1,5,5,5,5,3,4,9,9,2,2,7,7,7,7,3,3,19,5,5,1,1,4,16,6,3,5,5,5,6,2,2,5,5,18,8,2,1,1,2,2,1,2,2,2,5,5,5,5,8,8,8,1,1,4,8,1,7,2,1,4,4,1,1,1,1,4,8,8,4,4,6,4,8,3,8,3,3,3,3,4,1,1,2,9,1,8,8,7,7,7,1,4,4,4,6,6,4,4,4,9,9,9,2,3,7,1,1,1,1,3,3,19,7,7,7,13,2,2,6,3,6,1,5,4,3,1,3,3,2,3,5,3,6,1,2,2,2,1,4,6,6,6,2,6,6,6,6,3,5,4,1,4,3,12,4,3,4,2,4,4,1,3,3,8,2,12,9,7,5,1,9,8,1,8,5,5,4,4,3,3,3,4,4,3,3,2,5,7,7,7,1,1,1,1,9,8,1,1,4,4,1,2,5,4,1,1,1,4,2,2,1,6,15,5,7,7,2,2,4,4,3,3,8,8,1,6,6,3,4,4,9,8,8,8,7,1,7,7,1,1,1,2,5,5,5,6,4,4,7,5,5,3,3,4,3,9,9,19,8,3,3,3,1,2,2,7,7,3,5,6,1,4,4,4,2,2,7,7,3,3,4,4,1,5,4,3,6,6,4,6,6,2,7,16,6,6,6,9,9,5,7,7,2,6,6,1,6,16,9,8,8,4,4,4,9,9,3,2,7,6,6,6,6,5,5,5,8,18,6,1,1,1,1,2,2,2,7,1,8,8,1,1,2,5,5,3,3,3,1,2,2,2,3,2,5,2,1,1,2,2,7,1,1,3,1,2,2,6,6,2,8,2,2,2,2,1,8,7,7,3,3,7,2,1,7,3,1,5,8,1,3,8,8,1,1,1,9,9,9,8,8,15,5,5,1,1,8,8,6,4,1,7,8,1,1,1,2,2,3,3,10,5,5,5,7,8,7,8,1,1,4,3,6,6,2,2,6,6,6,3,3,2,1,8,3,3,3,1,1,1,1,8,2,3,2,2,10,2,2,5,5,1,8,4,1,6,7,7,7,3,3,5,1,1,6,9,9,9,6,1,1,1,4,4,6,1,5,1,1,5,5,5,2,1,1,1,5,10,3,2,1,1,6,6,6,7,1,1,3,3,16,1,1,2,2,1,1,9,5,4,1,4,4,2,2,5,2,6,6,2,5,5,4,7,1,3,2,2,10,2,4,4,4,1,1,2,3,7,7,2,2,5,4,4,4,1,1,1,17,7,2,8,1,8,1,8,8,7,7,3,9,3,3,5,1,1,1,7,1,10,6,1,4,7,2,4,4,6,4,6,1,6,5,1,1,2,2,3,3,5,2,3,5,1,5,6,2,7,7,5,5,5,2,3,3,2,12,7,6,1,10,1,1,4,8,1,4,8,2,2,3,3,8,7,5,2,7,7,2,2,4,4,8,1,4,4,3,3,8,8,2,2,8,6,6,6,8,4,2,7,1,2,1,8,6,17]</t>
   </si>
   <si>
     <t>100100_5</t>
@@ -157,7 +157,7 @@
     <t>[[10,14,9,8]]</t>
   </si>
   <si>
-    <t>[7,7,6,6,4,1,7,7,7,2,2,3,3,17,1,6,4,4,4,1,8,4,4,4,1,8,2,5,5,5,5,2,8,8,1,3,2,2,6,3,3,1,3,5,4,3,3,3,3,8,6,2,2,1,6,3,9,3,7,2,23,6,4,4,7,6,6,1,3,1,3,1,8,9,2,1,1,1,5,1,1,5,1,6,6,8,3,3,7,7,3,3,3,1,2,1,2,2,1,1,1,1,3,4,1,4,2,23,2,4,4,7,3,6,7,5,1,4,4,2,2,8,8,8,8,1,9,9,6,7,9,5,6,6,5,5,2,7,2,1,5,3,1,2,2,4,2,1,1,2,2,9,7,1,1,23,1,1,1,7,6,6,9,1,8,2,5,2,17,7,6,5,7,2,1,2,1,18,5,5,7,7,7,2,2,1,3,3,1,1,6,6,9,1,3,8,2,5,6,6,9,7,1,2,1,5,5,4,1,1,8,8,8,1,1,5,2,2,9,4,1,1,2,2,3,3,13,5,1,5,5,5,6,23,1,4,1,4,1,1,6,6,1,9,1,1,1,4,1,4,1,4,4,5,2,2,2,5,5,5,1,2,2,3,9,6,1,6,6,6,6,5,16,1,1,1,3,3,7,1,2,2,2,2,1,4,4,4,8,7,7,2,1,1,5,5,5,5,1,7,8,8,8,8,1,1,7,7,7,7,5,5,9,23,6,4,9,9,1,1,1,1,1,3,7,7,6,2,2,2,2,6,6,2,4,4,4,4,5,5,2,1,4,3,1,1,1,9,2,2,2,9,5,5,1,6,3,6,6,9,8,8,8,3,4,3,2,1,1,8,8,2,2,2,3,3,3,3,5,5,5,5,1,1,2,3,4,6,7,1,1,2,7,7,7,7,1,4,9,6,6,6,6,2,1,2,1,5,3,3,3,3,4,7,1,2,9,9,1,9,2,8,8,8,1,7,4,6,6,6,6,5,5,2,5,1,3,5,4,4,3,1,1,1,12,2,4,1,6,6,4,8,7,4,4,8,2,9,8,1,23,4,9,4,3,3,3,3,9,3,3,3,3,9,9,3,2,2,2,2,1,1,5,8,4,4,4,4,3,3,8,7,10,1,1,8,4,7,7,5,2,2,4,4,8,3,6,8,8,8,9,9,9,9,5,3,2,2,6,1,1,6,6,1,1,6,9,3,7,8,8,1,7,5,1,1,1,8,2,8,3,7,1,1,10,6,7,1,1,4,5,5,5,1,11,6,6,1,1,2,2,2,2,4,4,4,3,1,1,1,3,3,7,7,2,8,8,1,1,2,2,2,4,4,4,7,5,5,5,7,7,7,9,1,1,5,5,8,9,9,9,9,23,3,1,4,4,4,5,4,4,5,3,3,6,6,6,6,4,6,6,6,8,8,8,8,4,4,4,4,3,3,7,17,1,1,2,9,6,1,3,7,7,7,6,7,7,6,6,16,3,2,2,2,4,4,8,8,1,1,12,1,1,7,1,3,3,1,1,1,5,7,7,4,1,3,3,3,6,6,6,6,5,5,8,9,5,8,8,8,8,3,8,18,2,5,5,5,5,2,7,7,7,5,5,15,3,1,1,1,1,2,3,3,9,2,2,2,1,7,5,2,1,1,1,1,19,9,2,2,2,4,2,3,1,6,3,4,23,3,3,2,4,8,1,3,5,4,3,7,3,4,4,18,7,5,5,5,1,2,2,1,1,5,4,4,2,2,2,5,3,1,6,1,23,5,5,5,8,7,1,5,8,1,1,8,8,4,5,5,10,6,9,5,3,1,1,3,1,3,14,1,4,2,5,6,6,7,23,3,5,5,2,2,2,7,7,1,2,1,6,12,4,4,4,2,3,7,17,3,1,10,1,2,12,1,1,5,5,2,3,4,6,6,1,8,3,3,6,6,3,9,3,23,1,4,1,1,3,8,4,4,7,2,3,9,1,4,5,5,5,4,10,4,2,6,6,8,7,7,8,7,23,3,3,7,8,1,6,1,4,18,1,1,3,8,8,1,2,2,1,1,8,2,5,5,7,7,3,3,1,2,3,10,3,1,2,5,2,2,7,2,6,6,1,6,1,8,23,1,1,4,5,1,1,14,4,9,2,2,6,6,16,1,2,2,8,8,1,1,1,5,1,23,10,7,1,1,6,1,2,9,6,4,4,2,3,3,4,3,1,8,4,2,2,1,2,7,7,2,6,2,6,6,2,7,2,1,3,1,7,1,6,7,1,1,7,1,7,16]</t>
+    <t>[7,7,6,6,4,1,7,7,7,2,2,3,3,17,1,6,4,4,4,1,8,4,4,4,1,8,2,5,5,5,5,2,8,8,1,3,2,2,6,3,3,1,3,5,4,3,3,3,3,8,6,2,2,1,6,3,9,3,7,2,2,6,4,4,7,6,6,1,3,1,3,1,8,9,2,1,1,1,5,1,1,5,1,6,6,8,3,3,7,7,3,3,3,1,2,1,2,2,1,1,1,1,3,4,1,4,2,2,2,4,4,7,3,6,7,5,1,4,4,2,2,8,8,8,8,1,9,9,6,7,9,5,6,6,5,5,2,7,2,1,5,3,1,2,2,4,2,1,1,2,2,9,7,1,1,2,1,1,1,7,6,6,9,1,8,2,5,2,17,7,6,5,7,2,1,2,1,18,5,5,7,7,7,2,2,1,3,3,1,1,6,6,9,1,3,8,2,5,6,6,9,7,1,2,1,5,5,4,1,1,8,8,8,1,1,5,2,2,9,4,1,1,2,2,3,3,13,5,1,5,5,5,6,2,1,4,1,4,1,1,6,6,1,9,1,1,1,4,1,4,1,4,4,5,2,2,2,5,5,5,1,2,2,3,9,6,1,6,6,6,6,5,16,1,1,1,3,3,7,1,2,2,2,2,1,4,4,4,8,7,7,2,1,1,5,5,5,5,1,7,8,8,8,8,1,1,7,7,7,7,5,5,9,2,6,4,9,9,1,1,1,1,1,3,7,7,6,2,2,2,2,6,6,2,4,4,4,4,5,5,2,1,4,3,1,1,1,9,2,2,2,9,5,5,1,6,3,6,6,9,8,8,8,3,4,3,2,1,1,8,8,2,2,2,3,3,3,3,5,5,5,5,1,1,2,3,4,6,7,1,1,2,7,7,7,7,1,4,9,6,6,6,6,2,1,2,1,5,3,3,3,3,4,7,1,2,9,9,1,9,2,8,8,8,1,7,4,6,6,6,6,5,5,2,5,1,3,5,4,4,3,1,1,1,12,2,4,1,6,6,4,8,7,4,4,8,2,9,8,1,2,4,9,4,3,3,3,3,9,3,3,3,3,9,9,3,2,2,2,2,1,1,5,8,4,4,4,4,3,3,8,7,10,1,1,8,4,7,7,5,2,2,4,4,8,3,6,8,8,8,9,9,9,9,5,3,2,2,6,1,1,6,6,1,1,6,9,3,7,8,8,1,7,5,1,1,1,8,2,8,3,7,1,1,10,6,7,1,1,4,5,5,5,1,11,6,6,1,1,2,2,2,2,4,4,4,3,1,1,1,3,3,7,7,2,8,8,1,1,2,2,2,4,4,4,7,5,5,5,7,7,7,9,1,1,5,5,8,9,9,9,9,2,3,1,4,4,4,5,4,4,5,3,3,6,6,6,6,4,6,6,6,8,8,8,8,4,4,4,4,3,3,7,17,1,1,2,9,6,1,3,7,7,7,6,7,7,6,6,16,3,2,2,2,4,4,8,8,1,1,12,1,1,7,1,3,3,1,1,1,5,7,7,4,1,3,3,3,6,6,6,6,5,5,8,9,5,8,8,8,8,3,8,18,2,5,5,5,5,2,7,7,7,5,5,15,3,1,1,1,1,2,3,3,9,2,2,2,1,7,5,2,1,1,1,1,19,9,2,2,2,4,2,3,1,6,3,4,2,3,3,2,4,8,1,3,5,4,3,7,3,4,4,18,7,5,5,5,1,2,2,1,1,5,4,4,2,2,2,5,3,1,6,1,2,5,5,5,8,7,1,5,8,1,1,8,8,4,5,5,10,6,9,5,3,1,1,3,1,3,14,1,4,2,5,6,6,7,2,3,5,5,2,2,2,7,7,1,2,1,6,12,4,4,4,2,3,7,17,3,1,10,1,2,12,1,1,5,5,2,3,4,6,6,1,8,3,3,6,6,3,9,3,2,1,4,1,1,3,8,4,4,7,2,3,9,1,4,5,5,5,4,10,4,2,6,6,8,7,7,8,7,2,3,3,7,8,1,6,1,4,18,1,1,3,8,8,1,2,2,1,1,8,2,5,5,7,7,3,3,1,2,3,10,3,1,2,5,2,2,7,2,6,6,1,6,1,8,2,1,1,4,5,1,1,14,4,9,2,2,6,6,16,1,2,2,8,8,1,1,1,5,1,2,10,7,1,1,6,1,2,9,6,4,4,2,3,3,4,3,1,8,4,2,2,1,2,7,7,2,6,2,6,6,2,7,2,1,3,1,7,1,6,7,1,1,7,1,7,16]</t>
   </si>
 </sst>
 </file>
